--- a/members/A/experiment_log_A.xlsx
+++ b/members/A/experiment_log_A.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="실험로그" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="3주차_공통전처리" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,14 +17,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +52,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -579,4 +589,136 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="31" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>실험명</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>전처리</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>PR-AUC</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>common_preprocess.py 적용</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>0.6073298429319371</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.6137566137566137</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.6759271910100008</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Validation 기준, threshold=0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RandomOverSampler</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>common_preprocess.py 적용</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>0.7958115183246073</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.596078431372549</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.681332120685587</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Validation 기준, threshold=0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SMOTE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>common_preprocess.py 적용</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>0.774869109947644</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.6103092783505155</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.679619256317314</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Validation 기준, threshold=0.5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>